--- a/AAII_Financials/Yearly/NYC_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/NYC_YR_FIN.xlsx
@@ -3698,7 +3698,7 @@
         <v>11800</v>
       </c>
       <c r="E83" s="3">
-        <v>15900</v>
+        <v>15800</v>
       </c>
       <c r="F83" s="3">
         <v>22500</v>
